--- a/tame_output/ON/bt/strategyON_20240126.xlsx
+++ b/tame_output/ON/bt/strategyON_20240126.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.5%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.4%</t>
+          <t>101.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.6%</t>
+          <t>130.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1853"/>
+  <dimension ref="A1:G1854"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.23184816823649</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44180,6 +44180,29 @@
       </c>
       <c r="G1853" t="n">
         <v>4.498770500140957</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="2" t="n">
+        <v>45316</v>
+      </c>
+      <c r="B1854" t="n">
+        <v>3.236238754187724</v>
+      </c>
+      <c r="C1854" t="n">
+        <v>3.139547998939383</v>
+      </c>
+      <c r="D1854" t="n">
+        <v>1.651996231793977</v>
+      </c>
+      <c r="E1854" t="n">
+        <v>3.799990067343226</v>
+      </c>
+      <c r="F1854" t="n">
+        <v>2.265762155612401</v>
+      </c>
+      <c r="G1854" t="n">
+        <v>4.499005292306824</v>
       </c>
     </row>
   </sheetData>
